--- a/resources/templates/Template_TaxTool_FS_AI.xlsx
+++ b/resources/templates/Template_TaxTool_FS_AI.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istruzioni" sheetId="1" r:id="Re4d65ffdf79d4eb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anagrafica" sheetId="2" r:id="Re296a6f5a46f4991"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Voci IV Direttiva" sheetId="3" r:id="R567cd5ee6deb495d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stato Patrimoniale" sheetId="4" r:id="R0874819fdb184a6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conto Economico" sheetId="5" r:id="Rf9f0e64dee314871"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Esiti AI" sheetId="6" r:id="R68ae032bd5d04720"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istruzioni" sheetId="1" r:id="Ra7e97d88765f4668"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anagrafica" sheetId="2" r:id="R89a64b7133424878"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Voci IV Direttiva" sheetId="3" r:id="Rabdb7862f95d4a59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stato Patrimoniale" sheetId="4" r:id="Ra03edf12f2534d81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conto Economico" sheetId="5" r:id="R57d926d9c78f4d35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Esiti AI" sheetId="6" r:id="R0c56c6c3c63841b7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -119,9 +119,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -256,7 +256,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="2" t="str">
-        <x:v>TAX AUTOMATION LAB — RICLASSIFICA IV DIRETTIVA v1.3.3</x:v>
+        <x:v>TAX AUTOMATION LAB — RICLASSIFICA IV DIRETTIVA v1.3.4</x:v>
       </x:c>
     </x:row>
     <x:row r="2">

--- a/resources/templates/Template_TaxTool_FS_AI.xlsx
+++ b/resources/templates/Template_TaxTool_FS_AI.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istruzioni" sheetId="1" r:id="Ra7e97d88765f4668"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anagrafica" sheetId="2" r:id="R89a64b7133424878"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Voci IV Direttiva" sheetId="3" r:id="Rabdb7862f95d4a59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stato Patrimoniale" sheetId="4" r:id="Ra03edf12f2534d81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conto Economico" sheetId="5" r:id="R57d926d9c78f4d35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Esiti AI" sheetId="6" r:id="R0c56c6c3c63841b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istruzioni" sheetId="1" r:id="Re12f2f6ec3694db5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anagrafica" sheetId="2" r:id="R8a493d7f20054505"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Voci IV Direttiva" sheetId="3" r:id="Rc2b6b78cb9344054"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stato Patrimoniale" sheetId="4" r:id="R4288c6669e6349ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conto Economico" sheetId="5" r:id="R54350bac1d774681"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Esiti AI" sheetId="6" r:id="R6d17dd59a07b4258"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -256,7 +256,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="2" t="str">
-        <x:v>TAX AUTOMATION LAB — RICLASSIFICA IV DIRETTIVA v1.3.4</x:v>
+        <x:v>TAX AUTOMATION LAB — RICLASSIFICA IV DIRETTIVA v1.3.5</x:v>
       </x:c>
     </x:row>
     <x:row r="2">

--- a/resources/templates/Template_TaxTool_FS_AI.xlsx
+++ b/resources/templates/Template_TaxTool_FS_AI.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istruzioni" sheetId="1" r:id="Re12f2f6ec3694db5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anagrafica" sheetId="2" r:id="R8a493d7f20054505"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Voci IV Direttiva" sheetId="3" r:id="Rc2b6b78cb9344054"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stato Patrimoniale" sheetId="4" r:id="R4288c6669e6349ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conto Economico" sheetId="5" r:id="R54350bac1d774681"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Esiti AI" sheetId="6" r:id="R6d17dd59a07b4258"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istruzioni" sheetId="1" r:id="R54b8cc3323e34edd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anagrafica" sheetId="2" r:id="Rb894d93179b04956"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Voci IV Direttiva" sheetId="3" r:id="Rede716fbdd104b07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stato Patrimoniale" sheetId="4" r:id="Reb3ca8838bf146e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conto Economico" sheetId="5" r:id="R5a88d668becc481c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Esiti AI" sheetId="6" r:id="R049b93ebe3ff4c07"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -256,7 +256,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="2" t="str">
-        <x:v>TAX AUTOMATION LAB — RICLASSIFICA IV DIRETTIVA v1.3.5</x:v>
+        <x:v>TAX AUTOMATION LAB — RICLASSIFICA IV DIRETTIVA v1.3.6</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
